--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.61126134763757</v>
+        <v>7.411829968991104</v>
       </c>
       <c r="D2" t="n">
-        <v>47.91396898635963</v>
+        <v>7.786019960283441</v>
       </c>
       <c r="E2" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F2" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.32713231304619</v>
+        <v>6.065659000870006</v>
       </c>
       <c r="D3" t="n">
-        <v>26.86428889337793</v>
+        <v>4.365446945173914</v>
       </c>
       <c r="E3" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F3" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.26697134804706</v>
+        <v>6.380882844057648</v>
       </c>
       <c r="D4" t="n">
-        <v>26.01793241151809</v>
+        <v>4.22791401687169</v>
       </c>
       <c r="E4" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F4" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.39067535027176</v>
+        <v>4.938484744419161</v>
       </c>
       <c r="D5" t="n">
-        <v>29.68778170047689</v>
+        <v>4.824264526327494</v>
       </c>
       <c r="E5" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F5" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.01981766248009</v>
+        <v>2.765720370153015</v>
       </c>
       <c r="D6" t="n">
-        <v>29.97799726111435</v>
+        <v>4.871424554931082</v>
       </c>
       <c r="E6" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F6" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.714426023441</v>
+        <v>6.453594228809163</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11178423081199</v>
+        <v>7.005664937506949</v>
       </c>
       <c r="E7" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F7" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.52708882063996</v>
+        <v>5.123151933353994</v>
       </c>
       <c r="D8" t="n">
-        <v>9.300015154712279</v>
+        <v>1.511252462640745</v>
       </c>
       <c r="E8" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F8" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16313775001267</v>
+        <v>5.876509884377058</v>
       </c>
       <c r="D9" t="n">
-        <v>49.51570905276216</v>
+        <v>8.046302721073852</v>
       </c>
       <c r="E9" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F9" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.27160768764167</v>
+        <v>3.131636249241772</v>
       </c>
       <c r="D10" t="n">
-        <v>12.25329615076202</v>
+        <v>1.991160624498828</v>
       </c>
       <c r="E10" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F10" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.15409176674391</v>
+        <v>5.387539912095885</v>
       </c>
       <c r="D11" t="n">
-        <v>54.62866552708269</v>
+        <v>8.877158148150937</v>
       </c>
       <c r="E11" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F11" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.31177280223992</v>
+        <v>2.000663080363987</v>
       </c>
       <c r="D12" t="n">
-        <v>43.44350153313489</v>
+        <v>7.05956899913442</v>
       </c>
       <c r="E12" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F12" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>56.07697658442805</v>
+        <v>9.112508694969559</v>
       </c>
       <c r="D13" t="n">
-        <v>11.35420718829017</v>
+        <v>1.845058668097152</v>
       </c>
       <c r="E13" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F13" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.2682525206336</v>
+        <v>7.193591034602961</v>
       </c>
       <c r="D14" t="n">
-        <v>11.6192488760868</v>
+        <v>1.888127942364105</v>
       </c>
       <c r="E14" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F14" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.48779711226278</v>
+        <v>6.904267030742703</v>
       </c>
       <c r="D15" t="n">
-        <v>12.01041214946431</v>
+        <v>1.951691974287951</v>
       </c>
       <c r="E15" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F15" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.33590562489503</v>
+        <v>5.904584664045443</v>
       </c>
       <c r="D16" t="n">
-        <v>67.47369076443775</v>
+        <v>10.96447474922113</v>
       </c>
       <c r="E16" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F16" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.73163363140489</v>
+        <v>5.968890465103295</v>
       </c>
       <c r="D17" t="n">
-        <v>52.55949010407159</v>
+        <v>8.540917141911635</v>
       </c>
       <c r="E17" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F17" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.47845110359951</v>
+        <v>3.65274830433492</v>
       </c>
       <c r="D18" t="n">
-        <v>22.70128466654187</v>
+        <v>3.688958758313055</v>
       </c>
       <c r="E18" t="n">
-        <v>10.89177714756359</v>
+        <v>1.769913786479083</v>
       </c>
       <c r="F18" t="n">
-        <v>17.67295696212138</v>
+        <v>2.871855506344724</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
